--- a/etf_pilot/data/ETF汇总.xlsx
+++ b/etf_pilot/data/ETF汇总.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeffr\Documents\AI Projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeffr\Documents\AI Projects\etf_pilot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78ED2D11-A65B-4E36-8850-D931429FA760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DE0604-5903-4840-B3A3-4DD658D3E398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A25E0016-CBDC-4895-AB74-AEDB827AFCCA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
   <si>
     <t>指数简称</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>513100.SH</t>
-  </si>
-  <si>
-    <t>纳指达克ETF</t>
   </si>
   <si>
     <t>513300.SH</t>
@@ -558,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -593,10 +590,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -620,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -650,22 +647,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -679,10 +664,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1027,12 +1018,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
+      <c r="B1" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
@@ -1167,10 +1158,10 @@
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>23</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>24</v>
       </c>
       <c r="E12" s="14">
         <v>44140</v>
@@ -1179,10 +1170,10 @@
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>25</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="E13" s="14">
         <v>45091</v>
@@ -1191,10 +1182,10 @@
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="E14" s="14">
         <v>44776</v>
@@ -1203,10 +1194,10 @@
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>30</v>
       </c>
       <c r="E15" s="14">
         <v>45041</v>
@@ -1215,10 +1206,10 @@
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>32</v>
       </c>
       <c r="E16" s="14">
         <v>45135</v>
@@ -1227,10 +1218,10 @@
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" s="14">
         <v>45005</v>
@@ -1239,10 +1230,10 @@
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>34</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>35</v>
       </c>
       <c r="E18" s="14">
         <v>45163</v>
@@ -1251,10 +1242,10 @@
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>36</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>37</v>
       </c>
       <c r="E19" s="14">
         <v>45033</v>
@@ -1263,10 +1254,10 @@
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="E20" s="14">
         <v>45054</v>
@@ -1275,10 +1266,10 @@
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="7"/>
       <c r="C21" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="E21" s="10">
         <v>45232</v>
@@ -1286,13 +1277,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="E22" s="6">
         <v>43641</v>
@@ -1301,10 +1292,10 @@
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="11"/>
       <c r="C23" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="E23" s="14">
         <v>43641</v>
@@ -1313,10 +1304,10 @@
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="11"/>
       <c r="C24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="E24" s="14">
         <v>43641</v>
@@ -1325,10 +1316,10 @@
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="C25" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="E25" s="10">
         <v>44294</v>
@@ -1336,13 +1327,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="D26" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E26" s="3">
         <v>43641</v>
@@ -1350,13 +1341,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="D27" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="E27" s="6">
         <v>45412</v>
@@ -1365,10 +1356,10 @@
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="C28" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>46</v>
       </c>
       <c r="E28" s="10">
         <v>41887</v>
@@ -1376,13 +1367,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="D29" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E29" s="3">
         <v>43994</v>
@@ -1390,13 +1381,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="E30" s="6">
         <v>45489</v>
@@ -1405,10 +1396,10 @@
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="7"/>
       <c r="C31" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="E31" s="10">
         <v>45489</v>
@@ -1416,13 +1407,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="E32" s="6">
         <v>45974</v>
@@ -1431,10 +1422,10 @@
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="C33" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="E33" s="10">
         <v>45974</v>
@@ -1442,13 +1433,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="E34" s="6">
         <v>45708</v>
@@ -1456,13 +1447,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="D35" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="E35" s="14">
         <v>44925</v>
@@ -1470,13 +1461,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>97</v>
       </c>
       <c r="E36" s="14">
         <v>45261</v>
@@ -1484,13 +1475,13 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>100</v>
-      </c>
       <c r="D37" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E37" s="10">
         <v>44917</v>
@@ -1498,13 +1489,13 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="D38" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>77</v>
       </c>
       <c r="E38" s="14">
         <v>45245</v>
@@ -1513,10 +1504,10 @@
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="7"/>
       <c r="C39" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="E39" s="10">
         <v>45258</v>
@@ -1524,13 +1515,13 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="D40" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E40" s="3">
         <v>45324</v>
@@ -1538,13 +1529,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="D41" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E41" s="3">
         <v>45301</v>
@@ -1552,13 +1543,13 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="D42" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="E42" s="3">
         <v>45146</v>
@@ -1566,13 +1557,13 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="D43" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="E43" s="3">
         <v>44802</v>
@@ -1580,35 +1571,35 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="37" t="s">
+      <c r="D44" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="35"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="36"/>
+      <c r="C45" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D45" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E44" s="39"/>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="40"/>
-      <c r="C45" s="35" t="s">
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" s="38"/>
+      <c r="C46" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D46" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E45" s="41"/>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="42"/>
-      <c r="C46" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="E46" s="45"/>
+      <c r="E46" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
